--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.26764016696517</v>
+        <v>5.40599152713184</v>
       </c>
       <c r="D2" t="n">
-        <v>5.358624940939063</v>
+        <v>0.8707765529025978</v>
       </c>
       <c r="E2" t="n">
-        <v>7.848806914175345</v>
+        <v>1.275431123553494</v>
       </c>
       <c r="F2" t="n">
-        <v>6.18177969465325</v>
+        <v>1.004539200381153</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.24589481260715</v>
+        <v>4.264957907048662</v>
       </c>
       <c r="D3" t="n">
-        <v>24.56537425903581</v>
+        <v>3.99187331709332</v>
       </c>
       <c r="E3" t="n">
-        <v>7.848806914175345</v>
+        <v>1.275431123553494</v>
       </c>
       <c r="F3" t="n">
-        <v>6.18177969465325</v>
+        <v>1.004539200381153</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.64021026130146</v>
+        <v>4.816534167461488</v>
       </c>
       <c r="D4" t="n">
-        <v>27.50485517564012</v>
+        <v>4.469538966041519</v>
       </c>
       <c r="E4" t="n">
-        <v>7.848806914175345</v>
+        <v>1.275431123553494</v>
       </c>
       <c r="F4" t="n">
-        <v>6.18177969465325</v>
+        <v>1.004539200381153</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.32158308406229</v>
+        <v>2.002257251160122</v>
       </c>
       <c r="D5" t="n">
-        <v>24.08393317061345</v>
+        <v>3.913639140224686</v>
       </c>
       <c r="E5" t="n">
-        <v>7.848806914175345</v>
+        <v>1.275431123553494</v>
       </c>
       <c r="F5" t="n">
-        <v>6.18177969465325</v>
+        <v>1.004539200381153</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.759088936479883</v>
+        <v>0.6108519521779811</v>
       </c>
       <c r="D6" t="n">
-        <v>17.60774819265629</v>
+        <v>2.861259081306647</v>
       </c>
       <c r="E6" t="n">
-        <v>7.848806914175345</v>
+        <v>1.275431123553494</v>
       </c>
       <c r="F6" t="n">
-        <v>6.18177969465325</v>
+        <v>1.004539200381153</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.00657780874821</v>
+        <v>3.088568893921584</v>
       </c>
       <c r="D7" t="n">
-        <v>18.33712082089225</v>
+        <v>2.979782133394991</v>
       </c>
       <c r="E7" t="n">
-        <v>7.848806914175345</v>
+        <v>1.275431123553494</v>
       </c>
       <c r="F7" t="n">
-        <v>6.18177969465325</v>
+        <v>1.004539200381153</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>9.279125083762541</v>
+        <v>1.507857826111413</v>
       </c>
       <c r="D8" t="n">
-        <v>8.78443309976311</v>
+        <v>1.427470378711505</v>
       </c>
       <c r="E8" t="n">
-        <v>7.848806914175345</v>
+        <v>1.275431123553494</v>
       </c>
       <c r="F8" t="n">
-        <v>6.18177969465325</v>
+        <v>1.004539200381153</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.79865337533642</v>
+        <v>2.404781173492169</v>
       </c>
       <c r="D9" t="n">
-        <v>14.83922244175001</v>
+        <v>2.411373646784376</v>
       </c>
       <c r="E9" t="n">
-        <v>7.848806914175345</v>
+        <v>1.275431123553494</v>
       </c>
       <c r="F9" t="n">
-        <v>6.18177969465325</v>
+        <v>1.004539200381153</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.72659801452916</v>
+        <v>2.880572177360988</v>
       </c>
       <c r="D10" t="n">
-        <v>17.77298207913579</v>
+        <v>2.888109587859566</v>
       </c>
       <c r="E10" t="n">
-        <v>7.848806914175345</v>
+        <v>1.275431123553494</v>
       </c>
       <c r="F10" t="n">
-        <v>6.18177969465325</v>
+        <v>1.004539200381153</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.74968188129169</v>
+        <v>4.0218233057099</v>
       </c>
       <c r="D11" t="n">
-        <v>23.70590610179948</v>
+        <v>3.852209741542417</v>
       </c>
       <c r="E11" t="n">
-        <v>7.848806914175345</v>
+        <v>1.275431123553494</v>
       </c>
       <c r="F11" t="n">
-        <v>6.18177969465325</v>
+        <v>1.004539200381153</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>18.08591276042582</v>
+        <v>2.938960823569197</v>
       </c>
       <c r="D12" t="n">
-        <v>17.03510499322466</v>
+        <v>2.768204561399008</v>
       </c>
       <c r="E12" t="n">
-        <v>7.848806914175345</v>
+        <v>1.275431123553494</v>
       </c>
       <c r="F12" t="n">
-        <v>6.18177969465325</v>
+        <v>1.004539200381153</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.70301353765593</v>
+        <v>3.851739699869089</v>
       </c>
       <c r="D13" t="n">
-        <v>22.855258608924</v>
+        <v>3.71397952395015</v>
       </c>
       <c r="E13" t="n">
-        <v>7.848806914175345</v>
+        <v>1.275431123553494</v>
       </c>
       <c r="F13" t="n">
-        <v>6.18177969465325</v>
+        <v>1.004539200381153</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>16.70354934142653</v>
+        <v>2.714326767981811</v>
       </c>
       <c r="D14" t="n">
-        <v>15.24835488944128</v>
+        <v>2.477857669534207</v>
       </c>
       <c r="E14" t="n">
-        <v>7.848806914175345</v>
+        <v>1.275431123553494</v>
       </c>
       <c r="F14" t="n">
-        <v>6.18177969465325</v>
+        <v>1.004539200381153</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25379751234395</v>
+        <v>2.153742095755891</v>
       </c>
       <c r="D15" t="n">
-        <v>10.30776406404415</v>
+        <v>1.675011660407175</v>
       </c>
       <c r="E15" t="n">
-        <v>7.848806914175345</v>
+        <v>1.275431123553494</v>
       </c>
       <c r="F15" t="n">
-        <v>6.18177969465325</v>
+        <v>1.004539200381153</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>27.45444087985988</v>
+        <v>4.46134664297723</v>
       </c>
       <c r="D16" t="n">
-        <v>12.53411680546383</v>
+        <v>2.036793980887872</v>
       </c>
       <c r="E16" t="n">
-        <v>7.848806914175345</v>
+        <v>1.275431123553494</v>
       </c>
       <c r="F16" t="n">
-        <v>6.18177969465325</v>
+        <v>1.004539200381153</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
